--- a/diseases/d183/2026-2029.xlsx
+++ b/diseases/d183/2026-2029.xlsx
@@ -6874,12 +6874,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -6904,12 +6904,12 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -6952,40 +6952,185 @@
       </c>
       <c r="AV44" t="inlineStr">
         <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA44" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB44" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC44" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>D183</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>epidemic-typhus-fever</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Epidemic typhus fever</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>D183</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Epidemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>流行性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP45" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS45" t="inlineStr"/>
+      <c r="AT45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV45" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW44" t="inlineStr">
+      <c r="AW45" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
+      <c r="AX45" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY44" t="inlineStr">
+      <c r="AY45" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
+      <c r="AZ45" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA44" t="inlineStr">
+      <c r="BA45" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB44" t="inlineStr">
+      <c r="BB45" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC44" t="inlineStr">
+      <c r="BC45" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -7107,7 +7252,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
@@ -7117,7 +7262,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d183/2026-2029.xlsx
+++ b/diseases/d183/2026-2029.xlsx
@@ -7136,6 +7136,151 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>D183</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>epidemic-typhus-fever</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Epidemic typhus fever</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>D183</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Epidemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>流行性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP46" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr"/>
+      <c r="AT46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV46" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA46" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB46" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC46" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7169,7 +7314,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -7252,7 +7397,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10">
@@ -7262,7 +7407,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d183/2026-2029.xlsx
+++ b/diseases/d183/2026-2029.xlsx
@@ -7281,6 +7281,151 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>D183</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>epidemic-typhus-fever</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Epidemic typhus fever</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>D183</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Epidemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>流行性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP47" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS47" t="inlineStr"/>
+      <c r="AT47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV47" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA47" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB47" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC47" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7314,7 +7459,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -7397,7 +7542,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10">
@@ -7407,7 +7552,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d183/2026-2029.xlsx
+++ b/diseases/d183/2026-2029.xlsx
@@ -7426,6 +7426,296 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>D183</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>epidemic-typhus-fever</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Epidemic typhus fever</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>D183</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Epidemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>流行性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP48" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS48" t="inlineStr"/>
+      <c r="AT48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV48" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA48" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB48" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC48" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>D183</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>epidemic-typhus-fever</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Epidemic typhus fever</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>D183</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Epidemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>流行性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP49" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr"/>
+      <c r="AT49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV49" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA49" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB49" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC49" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7459,7 +7749,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -7542,7 +7832,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10">
@@ -7552,7 +7842,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d183/2026-2029.xlsx
+++ b/diseases/d183/2026-2029.xlsx
@@ -7599,12 +7599,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N49" t="n">
@@ -7677,40 +7677,185 @@
       </c>
       <c r="AV49" t="inlineStr">
         <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA49" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB49" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC49" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>D183</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>epidemic-typhus-fever</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Epidemic typhus fever</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>D183</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Epidemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>流行性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP50" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr"/>
+      <c r="AT50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV50" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW49" t="inlineStr">
+      <c r="AW50" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
+      <c r="AX50" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY49" t="inlineStr">
+      <c r="AY50" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
+      <c r="AZ50" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA49" t="inlineStr">
+      <c r="BA50" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB49" t="inlineStr">
+      <c r="BB50" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC49" t="inlineStr">
+      <c r="BC50" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -7832,7 +7977,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10">
@@ -7842,7 +7987,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d183/2026-2029.xlsx
+++ b/diseases/d183/2026-2029.xlsx
@@ -773,6 +773,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1510,6 +1515,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2247,6 +2257,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2984,6 +2999,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3721,6 +3741,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4606,6 +4631,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5331,6 +5361,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6201,6 +6236,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7071,6 +7111,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7794,6 +7839,11 @@
       <c r="S50" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">

--- a/diseases/d183/2026-2029.xlsx
+++ b/diseases/d183/2026-2029.xlsx
@@ -7911,6 +7911,151 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>D183</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>epidemic-typhus-fever</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Epidemic typhus fever</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>D183</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Epidemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>流行性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP51" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr"/>
+      <c r="AT51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV51" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA51" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB51" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC51" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7944,7 +8089,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -8027,7 +8172,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10">
@@ -8037,7 +8182,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11">
